--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBD010C-A61A-4710-94A6-40A7106FF4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60371A2-6BC8-4250-9911-B5E85492E935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -76,6 +76,25 @@
   <si>
     <t>意思</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bell desk</t>
+  </si>
+  <si>
+    <t>ベルデスク</t>
+  </si>
+  <si>
+    <t>行李服务台</t>
+  </si>
+  <si>
+    <t>accordingly</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それゆえに</t>
+  </si>
+  <si>
+    <t>因此</t>
   </si>
 </sst>
 </file>
@@ -449,7 +468,15 @@
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
@@ -475,11 +502,19 @@
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="36">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>2</v>
       </c>
@@ -778,6 +813,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60371A2-6BC8-4250-9911-B5E85492E935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DD933A-7D3F-4DED-9901-CB8614098D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="10200" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="27" r:id="rId1"/>
-    <sheet name="template" sheetId="20" r:id="rId2"/>
-    <sheet name="list" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="2" sheetId="28" r:id="rId2"/>
+    <sheet name="template" sheetId="20" r:id="rId3"/>
+    <sheet name="list" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="18">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -830,6 +831,419 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B43F3BB-B896-45FB-82A6-068DB32EE858}">
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="E8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="E9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="E11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="E12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="E13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="E14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="E15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="E16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="E17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="E18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="E19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="E20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="E21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="E22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="E23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="E24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="E25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="E26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="E27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="E28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="E29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="E30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="E31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{47A782B7-62A3-4BB4-8DB7-3F625689461E}">
+          <x14:formula1>
+            <xm:f>list!$A$1:$A$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:F40</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CA1652-010D-4CD5-B2DA-C4FE25700D32}">
   <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="18"/>
@@ -1182,7 +1596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A79A7F9-6C51-469C-A9B7-1B65800AEB29}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18"/>

--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DD933A-7D3F-4DED-9901-CB8614098D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45380504-9A58-4D07-91DC-ADCEDF5F62B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="10200" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-16200" windowWidth="14592" windowHeight="15576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="27" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="54">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -96,13 +96,220 @@
   </si>
   <si>
     <t>因此</t>
+  </si>
+  <si>
+    <t>acknowledging
+testament
+Tougher
+strengthening
+refining</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>感謝する
+〜の証
+より厳しい
+強める（つよめる）こと
+精製</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>谢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>见证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更艰难</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+加强
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精炼</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>realty
+Willow Creek</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不動産
+カリフォルニア州ウィロー・クリーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>listed at
+proximity</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>で売り出されている
+接近（せっきん）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vancouver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バンクーバー</t>
+  </si>
+  <si>
+    <t>温哥华</t>
+  </si>
+  <si>
+    <t>cypress</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>糸</t>
+  </si>
+  <si>
+    <t>boutique</t>
+  </si>
+  <si>
+    <t>高級専門店</t>
+  </si>
+  <si>
+    <t>entertainment</t>
+  </si>
+  <si>
+    <t>エンターテインメント</t>
+  </si>
+  <si>
+    <t>娱乐</t>
+  </si>
+  <si>
+    <t>無料プレゼント</t>
+  </si>
+  <si>
+    <t>免费抽奖</t>
+  </si>
+  <si>
+    <t>giveaways</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Catalonia</t>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カタルーニャ</t>
+  </si>
+  <si>
+    <t>加泰罗尼亚</t>
+  </si>
+  <si>
+    <t>expressive</t>
+  </si>
+  <si>
+    <t>表現豊かな</t>
+  </si>
+  <si>
+    <t>pieces</t>
+  </si>
+  <si>
+    <t>作品</t>
+  </si>
+  <si>
+    <t>convey</t>
+  </si>
+  <si>
+    <t>伝えています</t>
+  </si>
+  <si>
+    <t>a sense of</t>
+  </si>
+  <si>
+    <t>感覚</t>
+  </si>
+  <si>
+    <t>delicate</t>
+  </si>
+  <si>
+    <t>繊細な</t>
+  </si>
+  <si>
+    <t>evoke</t>
+  </si>
+  <si>
+    <t>呼び起こす</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,13 +338,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -152,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -164,6 +390,16 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D011DD9F-C5D4-4222-9446-32104BC980D5}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -570,246 +806,6 @@
         <v>4</v>
       </c>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="4">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="4">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="4">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="4">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="4">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="4">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="4">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="4">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="4">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="4">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="4">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -822,7 +818,7 @@
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:F40</xm:sqref>
+          <xm:sqref>E2:F10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -832,398 +828,427 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B43F3BB-B896-45FB-82A6-068DB32EE858}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="25.8984375" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="4"/>
+    <row r="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="68.400000000000006" customHeight="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4">
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" s="8" customFormat="1">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="E4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="E4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="54">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
       <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="36">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
       <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:9">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
       <c r="E8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
       <c r="E9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
       <c r="E10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
       <c r="E11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
       <c r="E12" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
       <c r="E13" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
       <c r="E14" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
       <c r="E15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
       <c r="E16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
       <c r="E17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
       <c r="E18" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
       <c r="E19" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
       <c r="E20" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
       <c r="E21" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
       <c r="E22" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
       <c r="E23" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
       <c r="E24" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
       <c r="E25" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
       <c r="E26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
       <c r="E27" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
       <c r="E28" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="1"/>
       <c r="E29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="1"/>
       <c r="E30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="1"/>
       <c r="E31" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="4">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="4">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="4">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="4">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="4">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="4">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="4">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="G31" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1235,7 +1260,7 @@
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:F40</xm:sqref>
+          <xm:sqref>E2:F31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1250,333 +1275,333 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="4"/>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4">
-        <v>32</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4">
-        <v>33</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4">
-        <v>34</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4">
-        <v>35</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4">
-        <v>36</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4">
-        <v>37</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4">
-        <v>38</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4">
-        <v>39</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4">
-        <v>40</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4">
-        <v>41</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4">
-        <v>42</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="4">
-        <v>43</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4">
-        <v>44</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="4">
-        <v>45</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="4">
-        <v>46</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="4">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="4">
-        <v>48</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="4">
-        <v>49</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="4">
-        <v>50</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="4">
-        <v>51</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="4">
-        <v>52</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="4">
-        <v>53</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="4">
-        <v>54</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="4">
-        <v>55</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="4">
-        <v>56</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="4">
-        <v>57</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="4">
-        <v>58</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="4">
-        <v>59</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="4">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="4">
-        <v>61</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="4">
-        <v>62</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="4">
-        <v>63</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="4">
-        <v>64</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="4">
-        <v>65</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="4">
-        <v>66</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="4">
-        <v>67</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="4">
-        <v>68</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="4">
-        <v>69</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="4">
-        <v>70</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1588,7 +1613,7 @@
           <x14:formula1>
             <xm:f>list!$A$1:$A$2</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:F40</xm:sqref>
+          <xm:sqref>B2:C40</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45380504-9A58-4D07-91DC-ADCEDF5F62B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEB57C0-1CD9-44A0-B9EE-11932F88CC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-16200" windowWidth="14592" windowHeight="15576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-16308" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="27" r:id="rId1"/>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -400,6 +400,11 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,14 +895,14 @@
       <c r="F3" s="2"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:9" s="8" customFormat="1">
-      <c r="A4" s="7">
+    <row r="4" spans="1:9" s="12" customFormat="1" ht="17.399999999999999" customHeight="1">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9"/>
+      <c r="E4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:9" ht="54">
       <c r="A5" s="4">
@@ -971,18 +976,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="4">
+    <row r="10" spans="1:9" s="8" customFormat="1">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" t="s">
+      <c r="E10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="8" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEB57C0-1CD9-44A0-B9EE-11932F88CC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3805ADB5-7AAC-40C0-AA5C-43FAA8F977B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-16308" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="27" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="85">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -304,6 +304,173 @@
   <si>
     <t>呼び起こす</t>
   </si>
+  <si>
+    <r>
+      <t>admire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>称賛</t>
+  </si>
+  <si>
+    <t>伝統的な職人技</t>
+  </si>
+  <si>
+    <t>craftsmanship</t>
+  </si>
+  <si>
+    <t>bites</t>
+  </si>
+  <si>
+    <t>軽い軽食</t>
+  </si>
+  <si>
+    <t>apparel</t>
+  </si>
+  <si>
+    <t>アパレル,衣服</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ballpark</t>
+  </si>
+  <si>
+    <t>野球場</t>
+  </si>
+  <si>
+    <r>
+      <t>filling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the stands</t>
+    </r>
+  </si>
+  <si>
+    <t>埋め尽くしていき</t>
+  </si>
+  <si>
+    <t>chanting</t>
+  </si>
+  <si>
+    <t>チャント</t>
+  </si>
+  <si>
+    <t>齐声呐喊</t>
+  </si>
+  <si>
+    <t>pitcher</t>
+  </si>
+  <si>
+    <t>投手</t>
+  </si>
+  <si>
+    <r>
+      <t>へ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>向かいます</t>
+    </r>
+  </si>
+  <si>
+    <t>heading down</t>
+  </si>
+  <si>
+    <t>dugout</t>
+  </si>
+  <si>
+    <t>選手席</t>
+  </si>
+  <si>
+    <t>insights</t>
+  </si>
+  <si>
+    <t>見解</t>
+  </si>
+  <si>
+    <t>matchup</t>
+  </si>
+  <si>
+    <t>対戦</t>
+  </si>
+  <si>
+    <r>
+      <t>Wanderlust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the Wild</t>
+    </r>
+  </si>
+  <si>
+    <t>旅への強い憧れ</t>
+  </si>
+  <si>
+    <t>gems</t>
+  </si>
+  <si>
+    <t>名所</t>
+  </si>
+  <si>
+    <r>
+      <t>curiosity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and care</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>好奇心</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>と（自然や文化への）思いやり</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -378,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -405,6 +572,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B43F3BB-B896-45FB-82A6-068DB32EE858}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="4" width="0" hidden="1" customWidth="1"/>
@@ -895,14 +1063,14 @@
       <c r="F3" s="2"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:9" s="12" customFormat="1" ht="17.399999999999999" customHeight="1">
-      <c r="A4" s="11">
+    <row r="4" spans="1:9" ht="17.399999999999999" customHeight="1">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="13"/>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="54">
       <c r="A5" s="4">
@@ -976,18 +1144,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="8" customFormat="1">
-      <c r="A10" s="7">
+    <row r="10" spans="1:9" s="12" customFormat="1">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="8" t="s">
+      <c r="E10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="12" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1090,7 +1258,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:9">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -1105,7 +1273,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:9">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -1120,7 +1288,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -1135,7 +1303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -1143,9 +1311,14 @@
         <v>4</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="G20" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -1153,19 +1326,29 @@
         <v>4</v>
       </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="4">
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="8" customFormat="1">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="F22" s="9"/>
+      <c r="G22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -1173,9 +1356,14 @@
         <v>4</v>
       </c>
       <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="G23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -1183,9 +1371,14 @@
         <v>2</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="G24" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1193,9 +1386,14 @@
         <v>4</v>
       </c>
       <c r="F25" s="2"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="G25" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -1203,9 +1401,17 @@
         <v>4</v>
       </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="G26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -1213,9 +1419,14 @@
         <v>4</v>
       </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="G27" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -1223,9 +1434,14 @@
         <v>2</v>
       </c>
       <c r="F28" s="2"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -1233,9 +1449,14 @@
         <v>4</v>
       </c>
       <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -1243,9 +1464,14 @@
         <v>2</v>
       </c>
       <c r="F30" s="2"/>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="G30" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -1253,7 +1479,36 @@
         <v>4</v>
       </c>
       <c r="F31" s="2"/>
-      <c r="G31" s="1"/>
+      <c r="G31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="G32" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8">
+      <c r="G33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8">
+      <c r="G34" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3805ADB5-7AAC-40C0-AA5C-43FAA8F977B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05621C05-22A3-41F1-AAE8-FD5846C2FDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -471,6 +471,78 @@
       <t>と（自然や文化への）思いやり</t>
     </r>
   </si>
+  <si>
+    <t>initial screening</t>
+  </si>
+  <si>
+    <t>初期選考</t>
+  </si>
+  <si>
+    <t>reaching out</t>
+  </si>
+  <si>
+    <t>連絡を取る</t>
+  </si>
+  <si>
+    <t>articulate</t>
+  </si>
+  <si>
+    <t>はっきりと説明する</t>
+  </si>
+  <si>
+    <t>reveal</t>
+  </si>
+  <si>
+    <t>明らかにする</t>
+  </si>
+  <si>
+    <t>having me</t>
+  </si>
+  <si>
+    <t>ご招待いただき</t>
+  </si>
+  <si>
+    <t>Aerospace</t>
+  </si>
+  <si>
+    <t>エアロスペース</t>
+  </si>
+  <si>
+    <t>through</t>
+  </si>
+  <si>
+    <t>を通じて</t>
+  </si>
+  <si>
+    <t>refine</t>
+  </si>
+  <si>
+    <t>向上/チューニング</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>正確さ</t>
+  </si>
+  <si>
+    <t>reentry</t>
+  </si>
+  <si>
+    <t>再突入</t>
+  </si>
+  <si>
+    <t>shaped</t>
+  </si>
+  <si>
+    <t>決定づけること</t>
+  </si>
+  <si>
+    <t>reusable</t>
+  </si>
+  <si>
+    <t>再利用可能な</t>
+  </si>
 </sst>
 </file>
 
@@ -545,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -567,11 +639,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1001,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B43F3BB-B896-45FB-82A6-068DB32EE858}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="4" width="0" hidden="1" customWidth="1"/>
@@ -1144,18 +1211,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="12" customFormat="1">
-      <c r="A10" s="11">
+    <row r="10" spans="1:9">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="12" t="s">
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1341,7 +1408,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9"/>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="11" t="s">
         <v>58</v>
       </c>
       <c r="H22" s="8" t="s">
@@ -1426,18 +1493,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="4">
+    <row r="28" spans="1:9" s="8" customFormat="1">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" t="s">
+      <c r="F28" s="9"/>
+      <c r="G28" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="8" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1508,6 +1575,102 @@
       </c>
       <c r="H34" s="10" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8">
+      <c r="G35" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8">
+      <c r="G36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8">
+      <c r="G37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H37" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" spans="7:8">
+      <c r="G38" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="7:8">
+      <c r="G39" t="s">
+        <v>93</v>
+      </c>
+      <c r="H39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="7:8">
+      <c r="G40" t="s">
+        <v>95</v>
+      </c>
+      <c r="H40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="7:8">
+      <c r="G41" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="7:8">
+      <c r="G42" t="s">
+        <v>99</v>
+      </c>
+      <c r="H42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="7:8">
+      <c r="G43" t="s">
+        <v>101</v>
+      </c>
+      <c r="H43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="7:8">
+      <c r="G44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="7:8">
+      <c r="G45" t="s">
+        <v>105</v>
+      </c>
+      <c r="H45" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="46" spans="7:8">
+      <c r="G46" t="s">
+        <v>107</v>
+      </c>
+      <c r="H46" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Toeic/part4/ReviewWords.xlsx
+++ b/Toeic/part4/ReviewWords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05621C05-22A3-41F1-AAE8-FD5846C2FDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99C50E0-0A8A-4DF3-91B5-FA97747BC718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
@@ -542,6 +542,12 @@
   </si>
   <si>
     <t>再利用可能な</t>
+  </si>
+  <si>
+    <t>brought in</t>
+  </si>
+  <si>
+    <t>入荷した</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B43F3BB-B896-45FB-82A6-068DB32EE858}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="4" width="0" hidden="1" customWidth="1"/>
@@ -1671,6 +1677,14 @@
       </c>
       <c r="H46" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="7:8">
+      <c r="G47" t="s">
+        <v>109</v>
+      </c>
+      <c r="H47" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
